--- a/astro-site/public/dl/chocolate-shop-checklist-templates/05-chocolate-shop-cleaning-checklist-maintenance.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/05-chocolate-shop-cleaning-checklist-maintenance.xlsx
@@ -706,7 +706,7 @@
     <row r="14">
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>▸ The "Quarterly &amp; Annual" tab covers what you hire out and what an inspection asks for in writing: pest control, hood exhaust (NFPA 96, only if you cook with grease), water-activity (aw) tests, food handler cards and CFPM, tempering and panning machine service, refrigeration (EPA 608), probe and scale calibration, extinguishers (OSHA), gas, insurance and POS / sales tax.</t>
+          <t>▸ The "Quarterly &amp; Annual" tab covers what you hire out and what an inspection asks for in writing: pest control, hood exhaust (NFPA 96, only if you cook with grease), water-activity (aw) tests, food handler cards and CFPM, tempering machine service (and panning machine, if you have one), refrigeration (EPA 608), probe and scale calibration, extinguishers (OSHA), gas, insurance and POS / sales tax.</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Check the precision scale with a test weight; the retail scale must be legal-for-trade (NTEP), inspected and sealed by your state weights and measures office</t>
+          <t>Check the precision scale with a test weight; the retail scale must be legal-for-trade (NTEP), inspected and sealed by your state or local (county/city) weights and measures office</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Lab tests by an outside lab: water activity (aw) of new ganaches and fillings, to set their shelf life and confirm which ones are TCS (FDA Food Code 1-201.10); water testing only if you are on a private well</t>
+          <t>Lab tests by an outside lab: water activity and pH of each new ganache or filling BEFORE it goes on sale, and again if the recipe changes, to set its shelf life and confirm whether it is TCS (FDA Food Code 1-201.10); water testing only if you are on a private well</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2041,7 +2041,7 @@
       <c r="E8" s="12" t="n"/>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Semiannual</t>
+          <t>Per new recipe</t>
         </is>
       </c>
       <c r="G8" s="13" t="n"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Food handler cards for all staff (renewals as your state or county requires) and a certified food protection manager on the team (FDA Food Code 2-102.12)</t>
+          <t>Food handler cards where your state or county requires them (renewals on its schedule) and a certified food protection manager on the team (FDA Food Code 2-102.12)</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Technician service on the tempering machine and panning machine: probes, heating elements, gaskets and auger wear</t>
+          <t>Technician service on the tempering machine (and panning machine, if you have one): probes, heating elements, gaskets and, on continuous machines, auger wear</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
